--- a/output/Data and Chart Outputs/cambodia_power_generation.xlsx
+++ b/output/Data and Chart Outputs/cambodia_power_generation.xlsx
@@ -1401,14 +1401,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Imports_MWh = Imports_Vietnam + Imports_Thailand + Imports_Laos (HV grid links plus MV border supplies; Imports_HV_MWh / Imports_MV_MWh split them), not in Total_MWh. Supply_MWh = Total_MWh + Imports_MWh (EAC's 'total energy available').</t>
+          <t>Imports_MWh = Imports_Vietnam + Imports_Thailand + Imports_Laos (HV grid links plus MV border supplies; Imports_HV_MWh / Imports_MV_MWh split them), not in Total_MWh. Supply_MWh = Total_MWh + Imports_MWh (EAC's 'total energy available'). Imports_Laos_MWh, Imports_MWh, Imports_HV_MWh and Supply_MWh all INCLUDE EDC's Lao hydro plant (e.g. 2024: Laos 2,872 GWh = 16.6 GWh at HV/MV in EAC's import table + 2,855.7 GWh plant; imports 4,525 = Vietnam 921 + Thailand 731 + Laos 2,872 = HV 4,052 + MV 472; supply 20,005 = generation 15,481 + imports 4,525 = EAC's generation in Cambodia 18,336 + table imports 1,669); Total_MWh never does.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Imports_Laos_EDC_hydro_MWh: from 2024 EAC counts EDC's dedicated hydro plant in Laos (460 MW, wired to the Cambodian grid) as EDC generation; here it is moved to imports from Laos so Hydro_MWh is Cambodian plants only (until 2023 EAC itself listed this energy as 'import from Laos at HV'). For a year from the salient features (which do not split it out) the plant's last reported output is used - an ESTIMATE, flagged on the Basis sheet, replaced when that year's annual report appears (Ember makes the same adjustment).</t>
+          <t>Imports_Laos_EDC_hydro_MWh: from 2024 EAC counts EDC's dedicated hydro plant in Laos (460 MW, wired to the Cambodian grid) as EDC generation; here it is moved to imports from Laos so Hydro_MWh is Cambodian plants only (until 2023 EAC itself listed this energy as 'import from Laos at HV'). For a year from the salient features (which do not split it out) the plant's last reported output is used - an ESTIMATE, flagged on the Basis sheet and by Laos_EDC_hydro_estimated = True, replaced when that year's annual report appears (Ember makes the same adjustment). This is why 2025 shows the same plant output as 2024.</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2445,35 +2445,40 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Laos_EDC_hydro_estimated</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Imports_HV_MWh</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Imports_MV_MWh</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Supply_MWh</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>IPP_MWh</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>EDC_MWh</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Other_licensees_MWh</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Solar_rooftop_MWh</t>
         </is>
@@ -2510,13 +2515,13 @@
       <c r="J2" t="n">
         <v>636885</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>456244</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>165285</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>15356</v>
       </c>
     </row>
@@ -2551,13 +2556,13 @@
       <c r="J3" t="n">
         <v>743231</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>450854</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>273298</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>19078</v>
       </c>
     </row>
@@ -2592,13 +2597,13 @@
       <c r="J4" t="n">
         <v>879374</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>625131</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>233450</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>20793</v>
       </c>
     </row>
@@ -2633,13 +2638,13 @@
       <c r="J5" t="n">
         <v>1087104</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>853992</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>208871</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>24241</v>
       </c>
     </row>
@@ -2674,13 +2679,13 @@
       <c r="J6" t="n">
         <v>1349316</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>1141270</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>171886</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>36160</v>
       </c>
     </row>
@@ -2715,13 +2720,13 @@
       <c r="J7" t="n">
         <v>1484112</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>1286470</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>160012</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>37629</v>
       </c>
     </row>
@@ -2756,13 +2761,13 @@
       <c r="J8" t="n">
         <v>1234594</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>1092976</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>100030</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>41588</v>
       </c>
     </row>
@@ -2797,13 +2802,13 @@
       <c r="J9" t="n">
         <v>968364</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>880764</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>46689</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>40911</v>
       </c>
     </row>
@@ -2850,22 +2855,22 @@
       <c r="N10" t="n">
         <v>6600</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>1449540</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>380240</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>2848320</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>917537</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>63180</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>37822</v>
       </c>
     </row>
@@ -2912,22 +2917,22 @@
       <c r="N11" t="n">
         <v>9010</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>1611630</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>492690</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>3527420</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>1305991</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>76903</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>40206</v>
       </c>
     </row>
@@ -2974,22 +2979,22 @@
       <c r="N12" t="n">
         <v>10730</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>1746090</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>535540</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>4051590</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>1694700</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>47670</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>27590</v>
       </c>
     </row>
@@ -3036,22 +3041,22 @@
       <c r="N13" t="n">
         <v>13770</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>1228600</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>574440</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>4861420</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>2995430</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>34710</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>28230</v>
       </c>
     </row>
@@ -3098,22 +3103,22 @@
       <c r="N14" t="n">
         <v>18310</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>942150</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>583940</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>6015360</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>4421860</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>16820</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>50590</v>
       </c>
     </row>
@@ -3160,22 +3165,22 @@
       <c r="N15" t="n">
         <v>37410</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>884020</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>666170</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>7033140</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>5346880</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>84180</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>51900</v>
       </c>
     </row>
@@ -3222,22 +3227,22 @@
       <c r="N16" t="n">
         <v>53560</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>796310</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>642840</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>8072840</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>6534850</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>43740</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>55100</v>
       </c>
     </row>
@@ -3284,22 +3289,22 @@
       <c r="N17" t="n">
         <v>65550</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>939490</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>627020</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>9738770</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>8047500</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>67710</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>57060</v>
       </c>
     </row>
@@ -3346,22 +3351,22 @@
       <c r="N18" t="n">
         <v>129230</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>2364290</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>698370</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>11737910</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>8335520</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>231310</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>108420</v>
       </c>
     </row>
@@ -3408,22 +3413,22 @@
       <c r="N19" t="n">
         <v>1762850</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>3264800</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>554850</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>12400760</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>8400810</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>115410</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>64890</v>
       </c>
     </row>
@@ -3470,22 +3475,22 @@
       <c r="N20" t="n">
         <v>2271550</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>2921210</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>463840</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>13097820</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9141120</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>521990</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>49640</v>
       </c>
     </row>
@@ -3532,22 +3537,22 @@
       <c r="N21" t="n">
         <v>2734350</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>4258810</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>540630</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>14896080</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>9762780</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>305860</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>28000</v>
       </c>
     </row>
@@ -3594,22 +3599,22 @@
       <c r="N22" t="n">
         <v>2558680</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>2942460</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>430740</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>16987230</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13332020</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>55860</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>226160</v>
       </c>
     </row>
@@ -3659,25 +3664,28 @@
       <c r="O23" t="n">
         <v>2855690</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4052470</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>472210</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>20005310</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>14757870</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>438910</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>283870</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>219180</v>
       </c>
     </row>
@@ -3727,10 +3735,13 @@
       <c r="O24" t="n">
         <v>2855690</v>
       </c>
-      <c r="R24" t="n">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
         <v>22095480</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>265690</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/cambodia_power_generation.xlsx
+++ b/output/Data and Chart Outputs/cambodia_power_generation.xlsx
@@ -160,6 +160,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Cambodia power generation by type (EAC, annual) (to 2025)</a:t>
             </a:r>
           </a:p>
@@ -463,6 +464,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Cambodia electricity supply: domestic generation and imports by country (EAC) (to 2025)</a:t>
             </a:r>
           </a:p>
@@ -682,6 +684,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Cambodia installed capacity by type (EAC, end of year) (to 2025)</a:t>
             </a:r>
           </a:p>
@@ -815,7 +818,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -843,7 +846,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -871,7 +874,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -899,7 +902,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1371,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1626,20 +1629,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Read: Annual-Report-2025-en.pdf | Last-Modified: Thu, 08 Oct 2026 02:32:43 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Read: salient_feature_2025_en.pdf | Last-Modified: Fri, 26 Dec 2025 07:36:43 GMT</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Electricity Authority of Cambodia (EAC): Report on Power Sector of the Kingdom of Cambodia (annual, Annex 2 tables) and Salient Features of Power Development in the Kingdom of Cambodia, https://eac.gov.kh/site/annualreport?lang=en</t>
         </is>
@@ -1813,7 +1823,7 @@
         <v>45658</v>
       </c>
       <c r="B6" t="n">
-        <v>5311.83</v>
+        <v>5667.51</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1822,16 +1832,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1831.72</v>
+        <v>2217.36</v>
       </c>
       <c r="F6" t="n">
-        <v>9828.08</v>
+        <v>9799.32</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>503.0700000000001</v>
+        <v>373.27</v>
       </c>
     </row>
   </sheetData>
@@ -2130,16 +2140,16 @@
         <v>45658</v>
       </c>
       <c r="B17" t="n">
-        <v>17474.7</v>
+        <v>18057.46</v>
       </c>
       <c r="C17" t="n">
-        <v>1191.28</v>
+        <v>1068.07</v>
       </c>
       <c r="D17" t="n">
-        <v>391.33</v>
+        <v>402.99</v>
       </c>
       <c r="E17" t="n">
-        <v>3038.17</v>
+        <v>3001.1</v>
       </c>
     </row>
   </sheetData>
@@ -2328,7 +2338,7 @@
         <v>45658</v>
       </c>
       <c r="B6" t="n">
-        <v>1.341</v>
+        <v>1.3414</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -2337,16 +2347,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.307</v>
+        <v>1.3706</v>
       </c>
       <c r="F6" t="n">
-        <v>0.569</v>
+        <v>0.6137</v>
       </c>
       <c r="G6" t="n">
-        <v>0.049</v>
+        <v>0.0492</v>
       </c>
       <c r="H6" t="n">
-        <v>1.365</v>
+        <v>1.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3694,7 +3704,7 @@
         <v>45658</v>
       </c>
       <c r="B24" t="n">
-        <v>5311830</v>
+        <v>5667510</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -3703,43 +3713,58 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1831720</v>
+        <v>2217360</v>
       </c>
       <c r="F24" t="n">
-        <v>9828080</v>
+        <v>9799320</v>
       </c>
       <c r="G24" t="n">
-        <v>450480</v>
+        <v>295520</v>
       </c>
       <c r="H24" t="n">
-        <v>52590</v>
+        <v>77750</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>17474700</v>
+        <v>18057460</v>
       </c>
       <c r="K24" t="n">
-        <v>4620780</v>
+        <v>4472160</v>
       </c>
       <c r="L24" t="n">
-        <v>1191280</v>
+        <v>1068070</v>
       </c>
       <c r="M24" t="n">
-        <v>391330</v>
+        <v>402990</v>
       </c>
       <c r="N24" t="n">
-        <v>3038170</v>
+        <v>3001100</v>
       </c>
       <c r="O24" t="n">
-        <v>2855690</v>
+        <v>2846080</v>
       </c>
       <c r="P24" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4076220</v>
+      </c>
+      <c r="R24" t="n">
+        <v>395940</v>
       </c>
       <c r="S24" t="n">
-        <v>22095480</v>
+        <v>22529620</v>
+      </c>
+      <c r="T24" t="n">
+        <v>17322730</v>
+      </c>
+      <c r="U24" t="n">
+        <v>219790</v>
+      </c>
+      <c r="V24" t="n">
+        <v>256980</v>
       </c>
       <c r="W24" t="n">
         <v>265690</v>
@@ -4244,22 +4269,22 @@
         <v>45658</v>
       </c>
       <c r="B24" t="n">
-        <v>1341</v>
+        <v>1341.4</v>
       </c>
       <c r="C24" t="n">
-        <v>569</v>
+        <v>613.7</v>
       </c>
       <c r="D24" t="n">
-        <v>4631</v>
+        <v>4774.9</v>
       </c>
       <c r="E24" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="F24" t="n">
-        <v>1365</v>
+        <v>1400</v>
       </c>
       <c r="G24" t="n">
-        <v>1307</v>
+        <v>1370.6</v>
       </c>
     </row>
   </sheetData>
@@ -4504,7 +4529,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EAC Report on Power Sector 2024 (Annex 2); hydro excludes EDC's dedicated Lao hydro plant (2,856 GWh), counted as imports from Laos</t>
+          <t>EAC Report on Power Sector 2025 (Annex 2); hydro excludes EDC's dedicated Lao hydro plant (2,856 GWh), counted as imports from Laos</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4539,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EAC Salient Features of Power Development 2025 (provisional until the annual report); ESTIMATE: hydro excludes EDC's dedicated Lao hydro plant at its 2024 output (2,856 GWh, moved to imports from Laos) - this publication does not split it out</t>
+          <t>EAC Report on Power Sector 2025 (Annex 2); hydro excludes EDC's dedicated Lao hydro plant (2,846 GWh), counted as imports from Laos</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E954"/>
+  <dimension ref="A1:E1014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23819,7 +23844,7 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B919" t="n">
@@ -23827,20 +23852,20 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>cap_Bioenergy</t>
+          <t>available_total</t>
         </is>
       </c>
       <c r="D919" t="n">
         <v>2024</v>
       </c>
       <c r="E919" t="n">
-        <v>49</v>
+        <v>20005.32</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B920" t="n">
@@ -23848,20 +23873,20 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>cap_Coal</t>
+          <t>cap_Bioenergy</t>
         </is>
       </c>
       <c r="D920" t="n">
         <v>2024</v>
       </c>
       <c r="E920" t="n">
-        <v>1300</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B921" t="n">
@@ -23869,20 +23894,20 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>cap_Hydro</t>
+          <t>cap_Coal</t>
         </is>
       </c>
       <c r="D921" t="n">
         <v>2024</v>
       </c>
       <c r="E921" t="n">
-        <v>1796</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B922" t="n">
@@ -23890,20 +23915,20 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>cap_Oil</t>
+          <t>cap_Hydro</t>
         </is>
       </c>
       <c r="D922" t="n">
         <v>2024</v>
       </c>
       <c r="E922" t="n">
-        <v>400</v>
+        <v>1796.4</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B923" t="n">
@@ -23911,20 +23936,20 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>cap_Solar</t>
+          <t>cap_Oil</t>
         </is>
       </c>
       <c r="D923" t="n">
         <v>2024</v>
       </c>
       <c r="E923" t="n">
-        <v>827</v>
+        <v>657.025</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B924" t="n">
@@ -23932,20 +23957,20 @@
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>cap_Solar_rooftop</t>
+          <t>cap_Solar</t>
         </is>
       </c>
       <c r="D924" t="n">
         <v>2024</v>
       </c>
       <c r="E924" t="n">
-        <v>139</v>
+        <v>796.8440000000001</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B925" t="n">
@@ -23953,20 +23978,20 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>capimp_Laos</t>
+          <t>cap_Total</t>
         </is>
       </c>
       <c r="D925" t="n">
         <v>2024</v>
       </c>
       <c r="E925" t="n">
-        <v>56</v>
+        <v>4633.769</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B926" t="n">
@@ -23974,20 +23999,20 @@
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>capimp_Thailand</t>
+          <t>gen_Bioenergy</t>
         </is>
       </c>
       <c r="D926" t="n">
         <v>2024</v>
       </c>
       <c r="E926" t="n">
-        <v>277</v>
+        <v>77.34999999999999</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B927" t="n">
@@ -23995,20 +24020,20 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>capimp_Vietnam</t>
+          <t>gen_Coal</t>
         </is>
       </c>
       <c r="D927" t="n">
         <v>2024</v>
       </c>
       <c r="E927" t="n">
-        <v>339</v>
+        <v>9428.139999999999</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B928" t="n">
@@ -24016,20 +24041,20 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>gen_Bioenergy</t>
+          <t>gen_Hydro</t>
         </is>
       </c>
       <c r="D928" t="n">
         <v>2024</v>
       </c>
       <c r="E928" t="n">
-        <v>66.66</v>
+        <v>7227.83</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B929" t="n">
@@ -24037,20 +24062,20 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>gen_Coal</t>
+          <t>gen_Oil</t>
         </is>
       </c>
       <c r="D929" t="n">
         <v>2024</v>
       </c>
       <c r="E929" t="n">
-        <v>9208.879999999999</v>
+        <v>532.98</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B930" t="n">
@@ -24058,20 +24083,20 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>gen_Hydro</t>
+          <t>gen_Solar</t>
         </is>
       </c>
       <c r="D930" t="n">
         <v>2024</v>
       </c>
       <c r="E930" t="n">
-        <v>7227.78</v>
+        <v>1070.02</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B931" t="n">
@@ -24079,20 +24104,20 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>gen_Oil</t>
+          <t>gen_Total</t>
         </is>
       </c>
       <c r="D931" t="n">
         <v>2024</v>
       </c>
       <c r="E931" t="n">
-        <v>532.42</v>
+        <v>18336.33</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B932" t="n">
@@ -24100,20 +24125,20 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>gen_Solar</t>
+          <t>gen_in_cambodia</t>
         </is>
       </c>
       <c r="D932" t="n">
         <v>2024</v>
       </c>
       <c r="E932" t="n">
-        <v>1059.78</v>
+        <v>18336.33</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B933" t="n">
@@ -24121,20 +24146,20 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>gen_Solar_rooftop</t>
+          <t>imp_Laos_HV</t>
         </is>
       </c>
       <c r="D933" t="n">
         <v>2024</v>
       </c>
       <c r="E933" t="n">
-        <v>219.18</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B934" t="n">
@@ -24142,20 +24167,20 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>imp_Laos</t>
+          <t>imp_Laos_MV</t>
         </is>
       </c>
       <c r="D934" t="n">
         <v>2024</v>
       </c>
       <c r="E934" t="n">
-        <v>16.68</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B935" t="n">
@@ -24163,20 +24188,20 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>imp_Thailand</t>
+          <t>imp_Thailand_HV</t>
         </is>
       </c>
       <c r="D935" t="n">
         <v>2024</v>
       </c>
       <c r="E935" t="n">
-        <v>731.01</v>
+        <v>602.8200000000001</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B936" t="n">
@@ -24184,20 +24209,20 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>imp_Vietnam</t>
+          <t>imp_Thailand_MV</t>
         </is>
       </c>
       <c r="D936" t="n">
         <v>2024</v>
       </c>
       <c r="E936" t="n">
-        <v>910.04</v>
+        <v>128.19</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B937" t="n">
@@ -24205,20 +24230,20 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>cap_Bioenergy</t>
+          <t>imp_Vietnam_HV</t>
         </is>
       </c>
       <c r="D937" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E937" t="n">
-        <v>49</v>
+        <v>586.41</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B938" t="n">
@@ -24226,20 +24251,20 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>cap_Coal</t>
+          <t>imp_Vietnam_MV</t>
         </is>
       </c>
       <c r="D938" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E938" t="n">
-        <v>1365</v>
+        <v>334.98</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B939" t="n">
@@ -24247,20 +24272,20 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>cap_Hydro</t>
+          <t>lcap_EDC</t>
         </is>
       </c>
       <c r="D939" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E939" t="n">
-        <v>1801</v>
+        <v>514.4499999999999</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B940" t="n">
@@ -24268,20 +24293,20 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>cap_Oil</t>
+          <t>lcap_EDC_Laos_hydro</t>
         </is>
       </c>
       <c r="D940" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E940" t="n">
-        <v>569</v>
+        <v>460</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B941" t="n">
@@ -24289,20 +24314,20 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>cap_Solar</t>
+          <t>lcap_IPP</t>
         </is>
       </c>
       <c r="D941" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E941" t="n">
-        <v>1307</v>
+        <v>3577.7</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B942" t="n">
@@ -24310,20 +24335,20 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>cap_Solar_rooftop</t>
+          <t>lcap_Other_licensees</t>
         </is>
       </c>
       <c r="D942" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E942" t="n">
-        <v>169</v>
+        <v>81.619</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B943" t="n">
@@ -24331,20 +24356,20 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>capimp_Laos</t>
+          <t>lcap_Total</t>
         </is>
       </c>
       <c r="D943" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E943" t="n">
-        <v>56</v>
+        <v>4633.769</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B944" t="n">
@@ -24352,20 +24377,20 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>capimp_Thailand</t>
+          <t>lic_EDC</t>
         </is>
       </c>
       <c r="D944" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E944" t="n">
-        <v>277</v>
+        <v>438.91</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B945" t="n">
@@ -24373,20 +24398,20 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>capimp_Vietnam</t>
+          <t>lic_EDC_Laos_hydro</t>
         </is>
       </c>
       <c r="D945" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E945" t="n">
-        <v>339</v>
+        <v>2855.69</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B946" t="n">
@@ -24394,20 +24419,20 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>gen_Bioenergy</t>
+          <t>lic_IPP</t>
         </is>
       </c>
       <c r="D946" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E946" t="n">
-        <v>52.59</v>
+        <v>14757.87</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B947" t="n">
@@ -24415,20 +24440,20 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>gen_Coal</t>
+          <t>lic_Other_licensees</t>
         </is>
       </c>
       <c r="D947" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E947" t="n">
-        <v>9828.08</v>
+        <v>283.87</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B948" t="n">
@@ -24436,20 +24461,20 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>gen_Hydro</t>
+          <t>lic_Total</t>
         </is>
       </c>
       <c r="D948" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E948" t="n">
-        <v>8167.52</v>
+        <v>18336.33</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B949" t="n">
@@ -24457,20 +24482,20 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>gen_Oil</t>
+          <t>available_total</t>
         </is>
       </c>
       <c r="D949" t="n">
         <v>2025</v>
       </c>
       <c r="E949" t="n">
-        <v>450.48</v>
+        <v>22529.62</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B950" t="n">
@@ -24478,20 +24503,20 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>gen_Solar</t>
+          <t>cap_Bioenergy</t>
         </is>
       </c>
       <c r="D950" t="n">
         <v>2025</v>
       </c>
       <c r="E950" t="n">
-        <v>1831.72</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B951" t="n">
@@ -24499,20 +24524,20 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>gen_Solar_rooftop</t>
+          <t>cap_Coal</t>
         </is>
       </c>
       <c r="D951" t="n">
         <v>2025</v>
       </c>
       <c r="E951" t="n">
-        <v>265.69</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B952" t="n">
@@ -24520,20 +24545,20 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>imp_Laos</t>
+          <t>cap_Hydro</t>
         </is>
       </c>
       <c r="D952" t="n">
         <v>2025</v>
       </c>
       <c r="E952" t="n">
-        <v>182.48</v>
+        <v>1801.4</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B953" t="n">
@@ -24541,20 +24566,20 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>imp_Thailand</t>
+          <t>cap_Oil</t>
         </is>
       </c>
       <c r="D953" t="n">
         <v>2025</v>
       </c>
       <c r="E953" t="n">
-        <v>391.33</v>
+        <v>613.6799999999999</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>Salient features 2025</t>
+          <t>Annual report 2025</t>
         </is>
       </c>
       <c r="B954" t="n">
@@ -24562,13 +24587,1273 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>imp_Vietnam</t>
+          <t>cap_Solar</t>
         </is>
       </c>
       <c r="D954" t="n">
         <v>2025</v>
       </c>
       <c r="E954" t="n">
+        <v>1370.634</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B955" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>cap_Total</t>
+        </is>
+      </c>
+      <c r="D955" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E955" t="n">
+        <v>5234.914</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B956" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>gen_Bioenergy</t>
+        </is>
+      </c>
+      <c r="D956" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E956" t="n">
+        <v>77.75</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B957" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>gen_Coal</t>
+        </is>
+      </c>
+      <c r="D957" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E957" t="n">
+        <v>9799.32</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>gen_Hydro</t>
+        </is>
+      </c>
+      <c r="D958" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E958" t="n">
+        <v>8513.59</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>gen_Oil</t>
+        </is>
+      </c>
+      <c r="D959" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E959" t="n">
+        <v>295.52</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>gen_Solar</t>
+        </is>
+      </c>
+      <c r="D960" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E960" t="n">
+        <v>2217.36</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>gen_Total</t>
+        </is>
+      </c>
+      <c r="D961" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E961" t="n">
+        <v>20903.53</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>gen_in_cambodia</t>
+        </is>
+      </c>
+      <c r="D962" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E962" t="n">
+        <v>20903.53</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B963" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>imp_Laos_HV</t>
+        </is>
+      </c>
+      <c r="D963" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E963" t="n">
+        <v>145.62</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>imp_Laos_MV</t>
+        </is>
+      </c>
+      <c r="D964" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E964" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B965" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>imp_Thailand_HV</t>
+        </is>
+      </c>
+      <c r="D965" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E965" t="n">
+        <v>317.15</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>imp_Thailand_MV</t>
+        </is>
+      </c>
+      <c r="D966" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E966" t="n">
+        <v>85.84</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>imp_Vietnam_HV</t>
+        </is>
+      </c>
+      <c r="D967" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E967" t="n">
+        <v>767.37</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B968" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>imp_Vietnam_MV</t>
+        </is>
+      </c>
+      <c r="D968" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E968" t="n">
+        <v>300.7</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>lcap_EDC</t>
+        </is>
+      </c>
+      <c r="D969" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E969" t="n">
+        <v>470.65</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B970" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>lcap_EDC_Laos_hydro</t>
+        </is>
+      </c>
+      <c r="D970" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E970" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B971" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>lcap_IPP</t>
+        </is>
+      </c>
+      <c r="D971" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E971" t="n">
+        <v>4057.9</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B972" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>lcap_Other_licensees</t>
+        </is>
+      </c>
+      <c r="D972" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E972" t="n">
+        <v>82.774</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>lcap_Total</t>
+        </is>
+      </c>
+      <c r="D973" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E973" t="n">
+        <v>5234.914</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>lic_EDC</t>
+        </is>
+      </c>
+      <c r="D974" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E974" t="n">
+        <v>219.79</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>lic_EDC_Laos_hydro</t>
+        </is>
+      </c>
+      <c r="D975" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E975" t="n">
+        <v>2846.08</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>lic_IPP</t>
+        </is>
+      </c>
+      <c r="D976" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E976" t="n">
+        <v>17322.73</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B977" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>lic_Other_licensees</t>
+        </is>
+      </c>
+      <c r="D977" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E977" t="n">
+        <v>256.98</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Annual report 2025</t>
+        </is>
+      </c>
+      <c r="B978" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>lic_Total</t>
+        </is>
+      </c>
+      <c r="D978" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E978" t="n">
+        <v>20903.53</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B979" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>cap_Bioenergy</t>
+        </is>
+      </c>
+      <c r="D979" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E979" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B980" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>cap_Coal</t>
+        </is>
+      </c>
+      <c r="D980" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E980" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B981" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>cap_Hydro</t>
+        </is>
+      </c>
+      <c r="D981" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E981" t="n">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B982" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>cap_Oil</t>
+        </is>
+      </c>
+      <c r="D982" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E982" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B983" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>cap_Solar</t>
+        </is>
+      </c>
+      <c r="D983" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E983" t="n">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B984" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>cap_Solar_rooftop</t>
+        </is>
+      </c>
+      <c r="D984" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E984" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B985" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>capimp_Laos</t>
+        </is>
+      </c>
+      <c r="D985" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E985" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B986" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>capimp_Thailand</t>
+        </is>
+      </c>
+      <c r="D986" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E986" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B987" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>capimp_Vietnam</t>
+        </is>
+      </c>
+      <c r="D987" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E987" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B988" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>gen_Bioenergy</t>
+        </is>
+      </c>
+      <c r="D988" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E988" t="n">
+        <v>66.66</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B989" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>gen_Coal</t>
+        </is>
+      </c>
+      <c r="D989" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E989" t="n">
+        <v>9208.879999999999</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B990" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>gen_Hydro</t>
+        </is>
+      </c>
+      <c r="D990" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E990" t="n">
+        <v>7227.78</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B991" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>gen_Oil</t>
+        </is>
+      </c>
+      <c r="D991" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E991" t="n">
+        <v>532.42</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B992" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>gen_Solar</t>
+        </is>
+      </c>
+      <c r="D992" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E992" t="n">
+        <v>1059.78</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B993" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>gen_Solar_rooftop</t>
+        </is>
+      </c>
+      <c r="D993" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E993" t="n">
+        <v>219.18</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B994" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>imp_Laos</t>
+        </is>
+      </c>
+      <c r="D994" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E994" t="n">
+        <v>16.68</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B995" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>imp_Thailand</t>
+        </is>
+      </c>
+      <c r="D995" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E995" t="n">
+        <v>731.01</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B996" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>imp_Vietnam</t>
+        </is>
+      </c>
+      <c r="D996" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E996" t="n">
+        <v>910.04</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B997" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>cap_Bioenergy</t>
+        </is>
+      </c>
+      <c r="D997" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E997" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B998" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>cap_Coal</t>
+        </is>
+      </c>
+      <c r="D998" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E998" t="n">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B999" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>cap_Hydro</t>
+        </is>
+      </c>
+      <c r="D999" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E999" t="n">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1000" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>cap_Oil</t>
+        </is>
+      </c>
+      <c r="D1000" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1001" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>cap_Solar</t>
+        </is>
+      </c>
+      <c r="D1001" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1002" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>cap_Solar_rooftop</t>
+        </is>
+      </c>
+      <c r="D1002" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1003" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>capimp_Laos</t>
+        </is>
+      </c>
+      <c r="D1003" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1004" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>capimp_Thailand</t>
+        </is>
+      </c>
+      <c r="D1004" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1005" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>capimp_Vietnam</t>
+        </is>
+      </c>
+      <c r="D1005" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1006" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>gen_Bioenergy</t>
+        </is>
+      </c>
+      <c r="D1006" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>52.59</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1007" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>gen_Coal</t>
+        </is>
+      </c>
+      <c r="D1007" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>9828.08</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1008" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>gen_Hydro</t>
+        </is>
+      </c>
+      <c r="D1008" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>8167.52</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1009" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>gen_Oil</t>
+        </is>
+      </c>
+      <c r="D1009" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>450.48</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1010" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>gen_Solar</t>
+        </is>
+      </c>
+      <c r="D1010" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>1831.72</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1011" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>gen_Solar_rooftop</t>
+        </is>
+      </c>
+      <c r="D1011" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>265.69</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1012" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>imp_Laos</t>
+        </is>
+      </c>
+      <c r="D1012" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>182.48</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1013" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>imp_Thailand</t>
+        </is>
+      </c>
+      <c r="D1013" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>391.33</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>Salient features 2025</t>
+        </is>
+      </c>
+      <c r="B1014" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>imp_Vietnam</t>
+        </is>
+      </c>
+      <c r="D1014" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E1014" t="n">
         <v>1191.28</v>
       </c>
     </row>
